--- a/artfynd/A 51514-2024 artfynd.xlsx
+++ b/artfynd/A 51514-2024 artfynd.xlsx
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98632561</v>
+        <v>98632550</v>
       </c>
       <c r="B2" t="n">
-        <v>56311</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562919.2837130409</v>
+        <v>562924</v>
       </c>
       <c r="R2" t="n">
-        <v>6433840.520219493</v>
+        <v>6433818</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,27 +744,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-24</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Sitter i grantopp. Brydde sig inte om tre helikoptrar som flög över sjön. AXN0071 (Calluna AB) spelflyktsinventering</t>
+          <t>Sittande i en grantopp, tittar sig mycket omkring. Bytte till en grantopp bredvid vid 10. Smet iväg vid 10.35 AXN0071 (Calluna AB) spelflyktsinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,19 +791,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98632550</v>
+        <v>98632561</v>
       </c>
       <c r="B3" t="n">
-        <v>56311</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -840,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562923.8939768934</v>
+        <v>562920</v>
       </c>
       <c r="R3" t="n">
-        <v>6433817.29655015</v>
+        <v>6433840</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -870,27 +860,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-16</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Sittande i en grantopp, tittar sig mycket omkring. Bytte till en grantopp bredvid vid 10. Smet iväg vid 10.35 AXN0071 (Calluna AB) spelflyktsinventering</t>
+          <t>Sitter i grantopp. Brydde sig inte om tre helikoptrar som flög över sjön. AXN0071 (Calluna AB) spelflyktsinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
